--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -838,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R3" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518738</v>
+        <v>124518643</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -960,7 +960,7 @@
         <v>591473</v>
       </c>
       <c r="R4" t="n">
-        <v>6447520</v>
+        <v>6447507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519119</v>
+        <v>124519348</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R5" t="n">
-        <v>6447485</v>
+        <v>6447456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518687</v>
+        <v>124518837</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591466</v>
+        <v>591455</v>
       </c>
       <c r="R6" t="n">
-        <v>6447503</v>
+        <v>6447514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519164</v>
+        <v>124518738</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591449</v>
+        <v>591473</v>
       </c>
       <c r="R7" t="n">
-        <v>6447463</v>
+        <v>6447520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519348</v>
+        <v>124519198</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591429</v>
+        <v>591439</v>
       </c>
       <c r="R8" t="n">
-        <v>6447456</v>
+        <v>6447464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518643</v>
+        <v>124518687</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591473</v>
+        <v>591466</v>
       </c>
       <c r="R9" t="n">
-        <v>6447507</v>
+        <v>6447503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519444</v>
+        <v>124519119</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,30 +1607,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591429</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447459</v>
+        <v>6447485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519198</v>
+        <v>124519164</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591439</v>
+        <v>591449</v>
       </c>
       <c r="R11" t="n">
-        <v>6447464</v>
+        <v>6447463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519444</v>
+        <v>124518837</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -838,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591429</v>
+        <v>591455</v>
       </c>
       <c r="R3" t="n">
-        <v>6447459</v>
+        <v>6447514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518643</v>
+        <v>124519301</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591473</v>
+        <v>591442</v>
       </c>
       <c r="R4" t="n">
-        <v>6447507</v>
+        <v>6447465</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519348</v>
+        <v>124518687</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591429</v>
+        <v>591466</v>
       </c>
       <c r="R5" t="n">
-        <v>6447456</v>
+        <v>6447503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518837</v>
+        <v>124518643</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591455</v>
+        <v>591473</v>
       </c>
       <c r="R6" t="n">
-        <v>6447514</v>
+        <v>6447507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519198</v>
+        <v>124519348</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591439</v>
+        <v>591429</v>
       </c>
       <c r="R8" t="n">
-        <v>6447464</v>
+        <v>6447456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518687</v>
+        <v>124519198</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591466</v>
+        <v>591439</v>
       </c>
       <c r="R9" t="n">
-        <v>6447503</v>
+        <v>6447464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519119</v>
+        <v>124519444</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,30 +1607,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R10" t="n">
-        <v>6447485</v>
+        <v>6447459</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519164</v>
+        <v>124519119</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591449</v>
+        <v>591442</v>
       </c>
       <c r="R11" t="n">
-        <v>6447463</v>
+        <v>6447485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519301</v>
+        <v>124519164</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591442</v>
+        <v>591449</v>
       </c>
       <c r="R12" t="n">
-        <v>6447465</v>
+        <v>6447463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518837</v>
+        <v>124518643</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,14 +838,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591455</v>
+        <v>591473</v>
       </c>
       <c r="R3" t="n">
-        <v>6447514</v>
+        <v>6447507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519301</v>
+        <v>124518837</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,14 +953,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591442</v>
+        <v>591455</v>
       </c>
       <c r="R4" t="n">
-        <v>6447465</v>
+        <v>6447514</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518687</v>
+        <v>124519164</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591466</v>
+        <v>591449</v>
       </c>
       <c r="R5" t="n">
-        <v>6447503</v>
+        <v>6447463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518643</v>
+        <v>124518687</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591473</v>
+        <v>591466</v>
       </c>
       <c r="R6" t="n">
-        <v>6447507</v>
+        <v>6447503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518738</v>
+        <v>124519444</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591473</v>
+        <v>591429</v>
       </c>
       <c r="R7" t="n">
-        <v>6447520</v>
+        <v>6447459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519348</v>
+        <v>124519198</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591429</v>
+        <v>591439</v>
       </c>
       <c r="R8" t="n">
-        <v>6447456</v>
+        <v>6447464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519198</v>
+        <v>124519301</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591439</v>
+        <v>591442</v>
       </c>
       <c r="R9" t="n">
-        <v>6447464</v>
+        <v>6447465</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519444</v>
+        <v>124519119</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,30 +1607,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591429</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447459</v>
+        <v>6447485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519119</v>
+        <v>124519348</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R11" t="n">
-        <v>6447485</v>
+        <v>6447456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519164</v>
+        <v>124518738</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591449</v>
+        <v>591473</v>
       </c>
       <c r="R12" t="n">
-        <v>6447463</v>
+        <v>6447520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518643</v>
+        <v>124519444</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591473</v>
+        <v>591429</v>
       </c>
       <c r="R3" t="n">
-        <v>6447507</v>
+        <v>6447459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518837</v>
+        <v>124518738</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -953,14 +953,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591455</v>
+        <v>591473</v>
       </c>
       <c r="R4" t="n">
-        <v>6447514</v>
+        <v>6447520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519164</v>
+        <v>124518643</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591449</v>
+        <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447463</v>
+        <v>6447507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518687</v>
+        <v>124518837</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591466</v>
+        <v>591455</v>
       </c>
       <c r="R6" t="n">
-        <v>6447503</v>
+        <v>6447514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519444</v>
+        <v>124519164</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R7" t="n">
-        <v>6447459</v>
+        <v>6447463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519301</v>
+        <v>124519348</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R9" t="n">
-        <v>6447465</v>
+        <v>6447456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519119</v>
+        <v>124518687</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,35 +1607,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591442</v>
+        <v>591466</v>
       </c>
       <c r="R10" t="n">
-        <v>6447485</v>
+        <v>6447503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519348</v>
+        <v>124519301</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591429</v>
+        <v>591442</v>
       </c>
       <c r="R11" t="n">
-        <v>6447456</v>
+        <v>6447465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124518738</v>
+        <v>124519119</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591473</v>
+        <v>591442</v>
       </c>
       <c r="R12" t="n">
-        <v>6447520</v>
+        <v>6447485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519444</v>
+        <v>124519164</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R3" t="n">
-        <v>6447459</v>
+        <v>6447463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518738</v>
+        <v>124518643</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -960,7 +960,7 @@
         <v>591473</v>
       </c>
       <c r="R4" t="n">
-        <v>6447520</v>
+        <v>6447507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518643</v>
+        <v>124518738</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447507</v>
+        <v>6447520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518837</v>
+        <v>124518687</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591455</v>
+        <v>591466</v>
       </c>
       <c r="R6" t="n">
-        <v>6447514</v>
+        <v>6447503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519164</v>
+        <v>124518837</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591449</v>
+        <v>591455</v>
       </c>
       <c r="R7" t="n">
-        <v>6447463</v>
+        <v>6447514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519198</v>
+        <v>124519119</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591439</v>
+        <v>591442</v>
       </c>
       <c r="R8" t="n">
-        <v>6447464</v>
+        <v>6447485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519348</v>
+        <v>124519444</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1535,7 +1535,7 @@
         <v>591429</v>
       </c>
       <c r="R9" t="n">
-        <v>6447456</v>
+        <v>6447459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124518687</v>
+        <v>124519301</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591466</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447503</v>
+        <v>6447465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519301</v>
+        <v>124519198</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591442</v>
+        <v>591439</v>
       </c>
       <c r="R11" t="n">
-        <v>6447465</v>
+        <v>6447464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519119</v>
+        <v>124519348</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,35 +1837,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R12" t="n">
-        <v>6447485</v>
+        <v>6447456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519164</v>
+        <v>124519119</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591449</v>
+        <v>591442</v>
       </c>
       <c r="R3" t="n">
-        <v>6447463</v>
+        <v>6447485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518643</v>
+        <v>124519198</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591473</v>
+        <v>591439</v>
       </c>
       <c r="R4" t="n">
-        <v>6447507</v>
+        <v>6447464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518738</v>
+        <v>124518643</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447520</v>
+        <v>6447507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R7" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519119</v>
+        <v>124519301</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,35 +1377,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         <v>591442</v>
       </c>
       <c r="R8" t="n">
-        <v>6447485</v>
+        <v>6447465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519444</v>
+        <v>124519164</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R9" t="n">
-        <v>6447459</v>
+        <v>6447463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519301</v>
+        <v>124518837</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1643,14 +1643,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591442</v>
+        <v>591455</v>
       </c>
       <c r="R10" t="n">
-        <v>6447465</v>
+        <v>6447514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519198</v>
+        <v>124519348</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591439</v>
+        <v>591429</v>
       </c>
       <c r="R11" t="n">
-        <v>6447464</v>
+        <v>6447456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519348</v>
+        <v>124518738</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591429</v>
+        <v>591473</v>
       </c>
       <c r="R12" t="n">
-        <v>6447456</v>
+        <v>6447520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519119</v>
+        <v>124519164</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591442</v>
+        <v>591449</v>
       </c>
       <c r="R3" t="n">
-        <v>6447485</v>
+        <v>6447463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518643</v>
+        <v>124518837</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591473</v>
+        <v>591455</v>
       </c>
       <c r="R5" t="n">
-        <v>6447507</v>
+        <v>6447514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518687</v>
+        <v>124519444</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591466</v>
+        <v>591429</v>
       </c>
       <c r="R6" t="n">
-        <v>6447503</v>
+        <v>6447459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519444</v>
+        <v>124518687</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591429</v>
+        <v>591466</v>
       </c>
       <c r="R7" t="n">
-        <v>6447459</v>
+        <v>6447503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519301</v>
+        <v>124518643</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591442</v>
+        <v>591473</v>
       </c>
       <c r="R8" t="n">
-        <v>6447465</v>
+        <v>6447507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519164</v>
+        <v>124518738</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591449</v>
+        <v>591473</v>
       </c>
       <c r="R9" t="n">
-        <v>6447463</v>
+        <v>6447520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124518837</v>
+        <v>124519301</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1643,14 +1643,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591455</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447514</v>
+        <v>6447465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124518738</v>
+        <v>124519119</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591473</v>
+        <v>591442</v>
       </c>
       <c r="R12" t="n">
-        <v>6447520</v>
+        <v>6447485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,14 +1068,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R5" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124519444</v>
+        <v>124518837</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591429</v>
+        <v>591455</v>
       </c>
       <c r="R6" t="n">
-        <v>6447459</v>
+        <v>6447514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519164</v>
+        <v>124518687</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591449</v>
+        <v>591466</v>
       </c>
       <c r="R3" t="n">
-        <v>6447463</v>
+        <v>6447503</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519198</v>
+        <v>124518738</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591439</v>
+        <v>591473</v>
       </c>
       <c r="R4" t="n">
-        <v>6447464</v>
+        <v>6447520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519444</v>
+        <v>124519164</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R5" t="n">
-        <v>6447459</v>
+        <v>6447463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518837</v>
+        <v>124519198</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591455</v>
+        <v>591439</v>
       </c>
       <c r="R6" t="n">
-        <v>6447514</v>
+        <v>6447464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518687</v>
+        <v>124519348</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591466</v>
+        <v>591429</v>
       </c>
       <c r="R7" t="n">
-        <v>6447503</v>
+        <v>6447456</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124518643</v>
+        <v>124518837</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1413,14 +1413,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591473</v>
+        <v>591455</v>
       </c>
       <c r="R8" t="n">
-        <v>6447507</v>
+        <v>6447514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518738</v>
+        <v>124519444</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591473</v>
+        <v>591429</v>
       </c>
       <c r="R9" t="n">
-        <v>6447520</v>
+        <v>6447459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519301</v>
+        <v>124518643</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591442</v>
+        <v>591473</v>
       </c>
       <c r="R10" t="n">
-        <v>6447465</v>
+        <v>6447507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519348</v>
+        <v>124519301</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591429</v>
+        <v>591442</v>
       </c>
       <c r="R11" t="n">
-        <v>6447456</v>
+        <v>6447465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518687</v>
+        <v>124519301</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591466</v>
+        <v>591442</v>
       </c>
       <c r="R3" t="n">
-        <v>6447503</v>
+        <v>6447465</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518738</v>
+        <v>124519198</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591473</v>
+        <v>591439</v>
       </c>
       <c r="R4" t="n">
-        <v>6447520</v>
+        <v>6447464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519164</v>
+        <v>124519348</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591449</v>
+        <v>591429</v>
       </c>
       <c r="R5" t="n">
-        <v>6447463</v>
+        <v>6447456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124519198</v>
+        <v>124518687</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591439</v>
+        <v>591466</v>
       </c>
       <c r="R6" t="n">
-        <v>6447464</v>
+        <v>6447503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519348</v>
+        <v>124518837</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591429</v>
+        <v>591455</v>
       </c>
       <c r="R7" t="n">
-        <v>6447456</v>
+        <v>6447514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124518837</v>
+        <v>124519119</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1413,14 +1413,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591455</v>
+        <v>591442</v>
       </c>
       <c r="R8" t="n">
-        <v>6447514</v>
+        <v>6447485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519444</v>
+        <v>124518643</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591429</v>
+        <v>591473</v>
       </c>
       <c r="R9" t="n">
-        <v>6447459</v>
+        <v>6447507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124518643</v>
+        <v>124519444</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591473</v>
+        <v>591429</v>
       </c>
       <c r="R10" t="n">
-        <v>6447507</v>
+        <v>6447459</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519301</v>
+        <v>124519164</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591442</v>
+        <v>591449</v>
       </c>
       <c r="R11" t="n">
-        <v>6447465</v>
+        <v>6447463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519119</v>
+        <v>124518738</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591442</v>
+        <v>591473</v>
       </c>
       <c r="R12" t="n">
-        <v>6447485</v>
+        <v>6447520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519301</v>
+        <v>124519119</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -845,7 +845,7 @@
         <v>591442</v>
       </c>
       <c r="R3" t="n">
-        <v>6447465</v>
+        <v>6447485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519198</v>
+        <v>124519164</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591439</v>
+        <v>591449</v>
       </c>
       <c r="R4" t="n">
-        <v>6447464</v>
+        <v>6447463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518687</v>
+        <v>124518837</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591466</v>
+        <v>591455</v>
       </c>
       <c r="R6" t="n">
-        <v>6447503</v>
+        <v>6447514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R7" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519119</v>
+        <v>124518738</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591442</v>
+        <v>591473</v>
       </c>
       <c r="R8" t="n">
-        <v>6447485</v>
+        <v>6447520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519444</v>
+        <v>124519301</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591429</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447459</v>
+        <v>6447465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519164</v>
+        <v>124519198</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591449</v>
+        <v>591439</v>
       </c>
       <c r="R11" t="n">
-        <v>6447463</v>
+        <v>6447464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124518738</v>
+        <v>124518687</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591473</v>
+        <v>591466</v>
       </c>
       <c r="R12" t="n">
-        <v>6447520</v>
+        <v>6447503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519119</v>
+        <v>124519348</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R3" t="n">
-        <v>6447485</v>
+        <v>6447456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519164</v>
+        <v>124519444</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591449</v>
+        <v>591429</v>
       </c>
       <c r="R4" t="n">
-        <v>6447463</v>
+        <v>6447459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519348</v>
+        <v>124518687</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591429</v>
+        <v>591466</v>
       </c>
       <c r="R5" t="n">
-        <v>6447456</v>
+        <v>6447503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518837</v>
+        <v>124518643</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591455</v>
+        <v>591473</v>
       </c>
       <c r="R6" t="n">
-        <v>6447514</v>
+        <v>6447507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519444</v>
+        <v>124519198</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591429</v>
+        <v>591439</v>
       </c>
       <c r="R7" t="n">
-        <v>6447459</v>
+        <v>6447464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124518738</v>
+        <v>124519164</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591473</v>
+        <v>591449</v>
       </c>
       <c r="R8" t="n">
-        <v>6447520</v>
+        <v>6447463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518643</v>
+        <v>124518837</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1528,14 +1528,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591473</v>
+        <v>591455</v>
       </c>
       <c r="R9" t="n">
-        <v>6447507</v>
+        <v>6447514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519198</v>
+        <v>124519119</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591439</v>
+        <v>591442</v>
       </c>
       <c r="R11" t="n">
-        <v>6447464</v>
+        <v>6447485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124518687</v>
+        <v>124518738</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591466</v>
+        <v>591473</v>
       </c>
       <c r="R12" t="n">
-        <v>6447503</v>
+        <v>6447520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519348</v>
+        <v>124518687</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591429</v>
+        <v>591466</v>
       </c>
       <c r="R3" t="n">
-        <v>6447456</v>
+        <v>6447503</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519444</v>
+        <v>124519348</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -960,7 +960,7 @@
         <v>591429</v>
       </c>
       <c r="R4" t="n">
-        <v>6447459</v>
+        <v>6447456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518687</v>
+        <v>124518738</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591466</v>
+        <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447503</v>
+        <v>6447520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518643</v>
+        <v>124519198</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591473</v>
+        <v>591439</v>
       </c>
       <c r="R6" t="n">
-        <v>6447507</v>
+        <v>6447464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124519198</v>
+        <v>124518643</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591439</v>
+        <v>591473</v>
       </c>
       <c r="R7" t="n">
-        <v>6447464</v>
+        <v>6447507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1528,14 +1528,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R9" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519119</v>
+        <v>124518837</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1758,14 +1758,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591442</v>
+        <v>591455</v>
       </c>
       <c r="R11" t="n">
-        <v>6447485</v>
+        <v>6447514</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124518738</v>
+        <v>124519119</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591473</v>
+        <v>591442</v>
       </c>
       <c r="R12" t="n">
-        <v>6447520</v>
+        <v>6447485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518687</v>
+        <v>124518738</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591466</v>
+        <v>591473</v>
       </c>
       <c r="R3" t="n">
-        <v>6447503</v>
+        <v>6447520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519348</v>
+        <v>124519164</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R4" t="n">
-        <v>6447456</v>
+        <v>6447463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518738</v>
+        <v>124519198</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591473</v>
+        <v>591439</v>
       </c>
       <c r="R5" t="n">
-        <v>6447520</v>
+        <v>6447464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124519198</v>
+        <v>124518687</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591439</v>
+        <v>591466</v>
       </c>
       <c r="R6" t="n">
-        <v>6447464</v>
+        <v>6447503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518643</v>
+        <v>124518837</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591473</v>
+        <v>591455</v>
       </c>
       <c r="R7" t="n">
-        <v>6447507</v>
+        <v>6447514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519164</v>
+        <v>124519348</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591449</v>
+        <v>591429</v>
       </c>
       <c r="R8" t="n">
-        <v>6447463</v>
+        <v>6447456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124519444</v>
+        <v>124518643</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591429</v>
+        <v>591473</v>
       </c>
       <c r="R9" t="n">
-        <v>6447459</v>
+        <v>6447507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124518837</v>
+        <v>124519444</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1758,14 +1758,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591455</v>
+        <v>591429</v>
       </c>
       <c r="R11" t="n">
-        <v>6447514</v>
+        <v>6447459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518738</v>
+        <v>124519348</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591473</v>
+        <v>591429</v>
       </c>
       <c r="R3" t="n">
-        <v>6447520</v>
+        <v>6447456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519164</v>
+        <v>124519119</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591449</v>
+        <v>591442</v>
       </c>
       <c r="R4" t="n">
-        <v>6447463</v>
+        <v>6447485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124519198</v>
+        <v>124518643</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591439</v>
+        <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447464</v>
+        <v>6447507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518687</v>
+        <v>124518738</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591466</v>
+        <v>591473</v>
       </c>
       <c r="R6" t="n">
-        <v>6447503</v>
+        <v>6447520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518837</v>
+        <v>124518687</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,14 +1298,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591455</v>
+        <v>591466</v>
       </c>
       <c r="R7" t="n">
-        <v>6447514</v>
+        <v>6447503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519348</v>
+        <v>124519444</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         <v>591429</v>
       </c>
       <c r="R8" t="n">
-        <v>6447456</v>
+        <v>6447459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518643</v>
+        <v>124518837</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1528,14 +1528,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591473</v>
+        <v>591455</v>
       </c>
       <c r="R9" t="n">
-        <v>6447507</v>
+        <v>6447514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519301</v>
+        <v>124519198</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591442</v>
+        <v>591439</v>
       </c>
       <c r="R10" t="n">
-        <v>6447465</v>
+        <v>6447464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519444</v>
+        <v>124519164</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591429</v>
+        <v>591449</v>
       </c>
       <c r="R11" t="n">
-        <v>6447459</v>
+        <v>6447463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519119</v>
+        <v>124519301</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,35 +1837,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
         <v>591442</v>
       </c>
       <c r="R12" t="n">
-        <v>6447485</v>
+        <v>6447465</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124519348</v>
+        <v>124519198</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,12 +825,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591429</v>
+        <v>591439</v>
       </c>
       <c r="R3" t="n">
-        <v>6447456</v>
+        <v>6447464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124519119</v>
+        <v>124519348</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591442</v>
+        <v>591429</v>
       </c>
       <c r="R4" t="n">
-        <v>6447485</v>
+        <v>6447456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518643</v>
+        <v>124518738</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         <v>591473</v>
       </c>
       <c r="R5" t="n">
-        <v>6447507</v>
+        <v>6447520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124518738</v>
+        <v>124519164</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591473</v>
+        <v>591449</v>
       </c>
       <c r="R6" t="n">
-        <v>6447520</v>
+        <v>6447463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124518687</v>
+        <v>124519444</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591466</v>
+        <v>591429</v>
       </c>
       <c r="R7" t="n">
-        <v>6447503</v>
+        <v>6447459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124519444</v>
+        <v>124518837</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1413,14 +1413,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillmossen, Sm</t>
+          <t>Lillmossen , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591429</v>
+        <v>591455</v>
       </c>
       <c r="R8" t="n">
-        <v>6447459</v>
+        <v>6447514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124518837</v>
+        <v>124519301</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1528,14 +1528,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmossen , Sm</t>
+          <t>Lillmossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591455</v>
+        <v>591442</v>
       </c>
       <c r="R9" t="n">
-        <v>6447514</v>
+        <v>6447465</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124519198</v>
+        <v>124519119</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591439</v>
+        <v>591442</v>
       </c>
       <c r="R10" t="n">
-        <v>6447464</v>
+        <v>6447485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124519164</v>
+        <v>124518687</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591449</v>
+        <v>591466</v>
       </c>
       <c r="R11" t="n">
-        <v>6447463</v>
+        <v>6447503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124519301</v>
+        <v>124518643</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591442</v>
+        <v>591473</v>
       </c>
       <c r="R12" t="n">
-        <v>6447465</v>
+        <v>6447507</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1938,6 +1938,126 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129874790</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591432</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6447456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tryserum</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>E-Val-0324</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sammanställt från 5 rapporter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Julie Goold</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 14192-2025 artfynd.xlsx
+++ b/artfynd/A 14192-2025 artfynd.xlsx
@@ -1943,7 +1943,7 @@
         <v>129874790</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
